--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.18258220808833</v>
+        <v>4.092169608814354</v>
       </c>
       <c r="D2" t="n">
-        <v>16.78211180081403</v>
+        <v>2.72709316763228</v>
       </c>
       <c r="E2" t="n">
-        <v>22.27252023795281</v>
+        <v>3.619284538667333</v>
       </c>
       <c r="F2" t="n">
-        <v>3.40794928546309</v>
+        <v>0.5537917588877521</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.00516337749271</v>
+        <v>10.72583904884257</v>
       </c>
       <c r="D3" t="n">
-        <v>23.30582702241883</v>
+        <v>3.78719689114306</v>
       </c>
       <c r="E3" t="n">
-        <v>22.27252023795281</v>
+        <v>3.619284538667333</v>
       </c>
       <c r="F3" t="n">
-        <v>3.40794928546309</v>
+        <v>0.5537917588877521</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.25011966915161</v>
+        <v>2.315644446237137</v>
       </c>
       <c r="D4" t="n">
-        <v>15.53349412891626</v>
+        <v>2.524192795948893</v>
       </c>
       <c r="E4" t="n">
-        <v>22.27252023795281</v>
+        <v>3.619284538667333</v>
       </c>
       <c r="F4" t="n">
-        <v>3.40794928546309</v>
+        <v>0.5537917588877521</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
